--- a/Other_Documents/Progress plan.xlsx
+++ b/Other_Documents/Progress plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Nexus\Other_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601A06E3-B91C-4F66-BC9C-8ECB3ED81BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8C4081-0E31-4C5B-8914-7A594F7B2097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>Date</t>
   </si>
@@ -125,6 +125,48 @@
   </si>
   <si>
     <t>I agent pick info, which is wrong then agent reditect to human to review, update the vector - selfheal AI</t>
+  </si>
+  <si>
+    <t>Project scaffolding</t>
+  </si>
+  <si>
+    <t>Day 4</t>
+  </si>
+  <si>
+    <t>Day 5</t>
+  </si>
+  <si>
+    <t>Day 7</t>
+  </si>
+  <si>
+    <t>Day 8</t>
+  </si>
+  <si>
+    <t>Rag Implementation SOW</t>
+  </si>
+  <si>
+    <t>Rag - Eval Harness and Questions</t>
+  </si>
+  <si>
+    <t>Rag Implementation - DB Se up</t>
+  </si>
+  <si>
+    <t>Nl2SQL Implementation</t>
+  </si>
+  <si>
+    <t>Day 9</t>
+  </si>
+  <si>
+    <t>Day 10</t>
+  </si>
+  <si>
+    <t>RAG + NL2SQL Integration</t>
+  </si>
+  <si>
+    <t>Single agent vs Agentic Implementation</t>
+  </si>
+  <si>
+    <t>treat rag and NL2SQL as diff tool to treat as agentic ai vs single agent</t>
   </si>
 </sst>
 </file>
@@ -547,7 +589,7 @@
         <v>46288</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
@@ -558,47 +600,120 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
+      <c r="B5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2">
+        <f>C4+1</f>
+        <v>46289</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="B6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46289</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46290</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46293</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46294</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46295</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="B11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46295</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46302</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">

--- a/Other_Documents/Progress plan.xlsx
+++ b/Other_Documents/Progress plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Nexus\Other_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8C4081-0E31-4C5B-8914-7A594F7B2097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3D75E3-680B-45D2-BC64-426B5568830F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Date</t>
   </si>
@@ -167,6 +167,28 @@
   </si>
   <si>
     <t>treat rag and NL2SQL as diff tool to treat as agentic ai vs single agent</t>
+  </si>
+  <si>
+    <t>Implement Redis</t>
+  </si>
+  <si>
+    <t>Better visibility of response to user</t>
+  </si>
+  <si>
+    <t>1. Live reasoning visibility (streaming)
+2. Response source indicator - Redis cache vs. full pipeline
+3. NL2SQL path indicator - semantic model vs. LLM-generated SQL
+4. SQL query shown for grounding, on BOTH paths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explore &amp; Implement Caching Strategy </t>
+  </si>
+  <si>
+    <t>1- Semantic cache (Implemented)
+2- Cache on metric and parameter on semnatic layer to skip database hit everytime for same question (Aspirational)</t>
   </si>
 </sst>
 </file>
@@ -216,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -234,6 +256,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,13 +539,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55" style="1" customWidth="1"/>
+    <col min="5" max="5" width="109.7109375" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -561,7 +586,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <f t="shared" ref="A3:A17" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A16" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -715,17 +740,44 @@
       <c r="C12" s="2">
         <v>46302</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46302</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46307</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -738,12 +790,6 @@
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <f t="shared" si="0"/>
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Other_Documents/Progress plan.xlsx
+++ b/Other_Documents/Progress plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Nexus\Other_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3D75E3-680B-45D2-BC64-426B5568830F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FE804B-95FD-4B97-9D2D-4A9276675610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>Date</t>
   </si>
@@ -189,6 +189,15 @@
   <si>
     <t>1- Semantic cache (Implemented)
 2- Cache on metric and parameter on semnatic layer to skip database hit everytime for same question (Aspirational)</t>
+  </si>
+  <si>
+    <t>Day 12</t>
+  </si>
+  <si>
+    <t>MCP Implementation</t>
+  </si>
+  <si>
+    <t>Call Tavily tool in Nuxus</t>
   </si>
 </sst>
 </file>
@@ -785,6 +794,18 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
+      <c r="B15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46308</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5">

--- a/Other_Documents/Progress plan.xlsx
+++ b/Other_Documents/Progress plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Nexus\Other_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FE804B-95FD-4B97-9D2D-4A9276675610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F66E79-BEF2-4249-938D-44FBD4B0B377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>Call Tavily tool in Nuxus</t>
+  </si>
+  <si>
+    <t>Day 13</t>
+  </si>
+  <si>
+    <t>Implement Guardrails</t>
+  </si>
+  <si>
+    <t>Guardrails at Direct prompt injection (input), Not use websearch as free llm (Input), Rag response groundedness (Output)</t>
   </si>
 </sst>
 </file>
@@ -812,6 +821,18 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
+      <c r="B16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
